--- a/sampling_protocol_v4.xlsx
+++ b/sampling_protocol_v4.xlsx
@@ -1403,12 +1403,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HOTEL &amp; APARTMENT VY VAN</t>
+          <t>Ocean Pearl Villa</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://www.booking.com/hotel/vn/amp-apartment-vy-van.html?aid=356938&amp;label=metagha-link-MRVN-hotel-10383270_dev-desktop_los-1_bw-10_dow-Wednesday_defdate-0_room-0_gstadt-2_rateid-0_aud-7380914326_gacid-21411118307_mcid-10_ppa-0_clrid-0_ad-1_gstkid-0_checkin-20250924_ppt-_lp-2704_r-12456579030551460187&amp;sid=44d60f09dd88b24d5cca2032942ebcb9&amp;all_sr_blocks=1038327003_376329923_2_0_0&amp;checkin=2025-09-24&amp;checkout=2025-09-25&amp;dest_id=10383270&amp;dest_type=hotel&amp;dist=0&amp;group_adults=2&amp;group_children=0&amp;hapos=1&amp;highlighted_blocks=1038327003_376329923_2_0_0&amp;hpos=1&amp;matching_block_id=1038327003_376329923_2_0_0&amp;no_rooms=1&amp;req_adults=2&amp;req_children=0&amp;room1=A%2CA&amp;sb_price_type=total&amp;sr_order=popularity&amp;sr_pri_blocks=1038327003_376329923_2_0_0__25000000&amp;srepoch=1757866195&amp;srpvid=1a2171941f9509a9&amp;type=total&amp;ucfs=1&amp;</t>
+          <t>https://www.booking.com/hotel/vn/ocean-pearl-villa-vung-tau.vi.html?aid=304142&amp;dest_id=-3733750&amp;dest_type=city&amp;checkin=2026-09-20&amp;checkout=2026-09-21&amp;group_adults=2&amp;group_children=0&amp;no_rooms=1&amp;selected_currency=VND&amp;lang=vi</t>
         </is>
       </c>
     </row>
